--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/elder_exile.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/elder_exile.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="raphael" sheetId="1" r:id="rId3"/>
+    <sheet name="raphael" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="131">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -487,154 +487,6 @@
   <si>
     <t xml:space="preserve">last</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">#race穿过结界到了这个村子…？
-原来如此，是那个小子出的主意吧。嘻嘻嘻…他确实不再需要「手环」了。毕竟就连我们伟大的主人伊兹帕鲁特大人都已经抛弃了他。
-也罢，这村子远离尘世，也总有些自己才知道的麻烦事。如果外人来了能派上些用场，就让他们来吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">请和我讲讲伊斯西泽尔吧</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你知道伊斯西泽尔吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">发现了迪伯妮但是…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于牛头人的大角</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我带回了迪伯妮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我杀了迪伯妮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迪伯妮不知去了哪里</t>
-  </si>
-  <si>
-    <t xml:space="preserve">暗之畸形「伊斯西泽尔」。嘻嘻嘻…这个村子怎会有人不知道这名字？
-在他的灵魂被不净之物玷污前，可是被誉为最接近神灵的魔法师。
-你们招惹了麻烦的敌人。就算是我们也没有能与他对抗的手段。就算是有办法，我们也不会参与这场世俗的纷争。说到底，流放者只对怎么赎罪感兴趣。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过…嘻嘻嘻…你也不必急着走…，眼下正好有适合交给你这种冒险者做的工作。如果你能顺利完成的话，也可授予你所渴求的「知识」。我们自古传承的秘术的配方，也许能成为用来击退伊斯西泽尔的武器。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嘻嘻嘻…好吧，从哪里开始讲呢。
-你知道吗？这个村子的东南方有个叫露里耶的神殿。众神从地上离去之后，露里耶神殿如今只能可悲地沉入海底…在我还是人类的时候，曾在那个神殿生活过。
-神殿里不知从哪里迷路来了一只暴食海狮幼崽，它叫迪伯妮，对我很亲近。虽然是个愚蠢又贪吃的家伙…嘻嘻嘻…但我对那笨拙可爱的小东西倾注了多到不可思议的感情。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">后来我迎来了死亡，但因生前的罪孽，我注定要在这个村子里无尽地赎罪。而这都已经是几千年前的事了。
-从那之后已经度过了漫长的岁月。但不可思议的是…哦哦，时至今日，我还感觉得到！迪伯妮还活着！
-嘻嘻嘻…我可以听到，那孩子被遗忘在海底发出的悲鸣。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">希望你能把迪伯妮从那深水之狱中带回来。
-我不知道那孩子依旧是海狮，还是变成了什么怪物…。如果它已经没有了获救的希望，就请你让那只悲伤的野兽永远的安息。这就是我的愿望。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嘻嘻嘻…话说回来，它还真是个笨孩子。都有本事活几千年，为什么还要留在那废墟中…嘻嘻嘻…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迪伯妮，变成了巨大的龙…？
-这可真是奇怪…我记得它确实是暴食海狮的幼崽…不对，人类时的记忆，早就淡去了。
-但不管怎么说，变成那种庞然大物，也不容易带回来了吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果用古老的魔道具「龙捕获球」的话，也许可以捕捉到迪伯妮。
-但是…嘻嘻嘻…很不凑巧，这个村子里缺乏制作的材料。
-它需要被称为「牛头人的大角」的稀有素材…说起来，有一群牛头人在约恩村南边筑了巢呢，嘻嘻嘻…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦哦，你拿的那不就是「牛头人的大角」吗？
-嘻嘻嘻…这样就能制作出把迪伯妮带回来的捕获球了。
-捕获球的使用方法，就不用对你这样的冒险者说明了吧。嘻嘻嘻…用手拿着丢向对方就可以。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迪伯妮它…这样啊…既然你觉得应该这么做，我也不说什么了。
-在这几千年的岁月里，那孩子为什么一直留在露里耶的废墟…算了，现在再去追究也没什么意义了。嘻嘻嘻…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嘻嘻嘻…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…不用担心。我没有忘记和你的约定。
-﻿
-接下来就把自古传承下来的秘术配方传授给你。卢恩铸造…这是人世间失传已久的宝贵知识。在和伊斯西泽尔的战斗中，它一定能帮到你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我们之间的交易结束了。好了，你可以走了，嘻嘻嘻…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…迪伯妮！　真的是迪伯妮吗！？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咕嗷嗷嗷嗷嗷嗷！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦哦，何等恐怖的咆哮！ 是想吃了我吗…？ 
-嘻嘻嘻…真有精神。我想，你大概已经把我给忘了吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咕嗷嗷嗷嗷嗷嗷嗷嗷嗷嗷！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…没想到，你原来是只龙啊。
-看到你这么精神的样子，我就满足了。老朽这条烂命死不足惜。来吧，随你喜欢吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咕嗷…咕噜噜……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迪伯妮...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咕噜咕噜…咕……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迪伯妮，难道说，你还记得我吗？
-啊…！　你脖子上的蝴蝶结，是我还是人类的时候开玩笑给你戴上的…
-你竟然如此珍惜它…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咕噜…咕噜…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迪伯妮，这样啊…原来是这样啊，嘻嘻嘻…
-我把你留在了海底，自己则被囚禁在无尽的赎罪中。但时隔千年，你还是没有抛弃我吗。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咕噜…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…原谅愚蠢的我吧，迪伯妮。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咕噜……咕嗷嗷嗷……！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦哦，迪伯妮...!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…嘻嘻嘻、不用担心。我没有忘记和你的约定。
-接下来就把自古传承下来的秘术配方传授给你。卢恩铸造…这是从人世间失传已久的宝贵知识。在和伊斯西泽尔的战斗中，它一定能帮到你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好了，迪伯妮。我要快点把你介绍给村里的其他人！
-嘻嘻嘻…不用害怕。大家虽然脸长的很诡异，但都不是坏人。你一定会成为村子里的大明星。
-过来，迪伯妮，来这边。以后我们就一起生活下去，…就像在露里耶的那个时候一样…嘻嘻嘻……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当伊斯西泽尔还是人类的时候，王侯贵族都曾争着乞求他的帮助。嘻嘻嘻…凭他强大的魔力，想支配大地上的王国也仅是不值得一提的小事罢了。
-伊斯西泽尔至今都甘愿在朽烂的古城夜以继日地研究魔石，换句话说，人类世界的权力也好名声也罢，对他而言都与尘埃无异。
-别忘了这点。你们将要面对的敌人，是超脱俗世纷争之人。你们正要叩响神话的大门。</t>
-  </si>
 </sst>
 </file>
 
@@ -654,19 +506,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -685,7 +537,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -718,7 +570,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -727,86 +579,86 @@
     </border>
   </borders>
   <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -816,18 +668,18 @@
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Excel Built-in Normal" xfId="20" builtinId="0"/>
+    <cellStyle name="Excel Built-in Normal" xfId="20"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1003,26 +855,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L115"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.55" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1060,24 +912,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="79.85">
-      <c r="I8" s="1">
+    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -1086,23 +938,20 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" ht="12.8">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1112,7 +961,7 @@
       <c r="E12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="1" t="n">
         <v>41</v>
       </c>
       <c r="J12" s="5" t="s">
@@ -1121,11 +970,8 @@
       <c r="K12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" ht="12.8">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1135,7 +981,7 @@
       <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J13" s="5" t="s">
@@ -1144,11 +990,8 @@
       <c r="K13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="14" ht="12.8">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
@@ -1161,7 +1004,7 @@
       <c r="E14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J14" s="5" t="s">
@@ -1170,11 +1013,8 @@
       <c r="K14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" ht="12.8">
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
@@ -1187,7 +1027,7 @@
       <c r="E15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J15" s="5" t="s">
@@ -1196,11 +1036,8 @@
       <c r="K15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" ht="12.8">
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -1210,7 +1047,7 @@
       <c r="E16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -1219,11 +1056,8 @@
       <c r="K16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="17" ht="12.8">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
         <v>38</v>
       </c>
@@ -1233,7 +1067,7 @@
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J17" s="5" t="s">
@@ -1242,11 +1076,8 @@
       <c r="K17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" ht="12.8">
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
@@ -1256,7 +1087,7 @@
       <c r="E18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J18" s="5" t="s">
@@ -1265,15 +1096,12 @@
       <c r="K18" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E20" s="1" t="s">
         <v>45</v>
       </c>
@@ -1281,23 +1109,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E22" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E23" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" ht="12.8">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" ht="113.4">
-      <c r="I28" s="1">
+    <row r="28" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J28" s="7" t="s">
@@ -1306,12 +1134,9 @@
       <c r="K28" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L28" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" ht="13.8">
-      <c r="I29" s="1">
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J29" s="9" t="s">
@@ -1320,12 +1145,9 @@
       <c r="K29" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L29" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" ht="113.4">
-      <c r="I30" s="1">
+    </row>
+    <row r="30" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="1" t="n">
         <v>40</v>
       </c>
       <c r="J30" s="7" t="s">
@@ -1334,12 +1156,9 @@
       <c r="K30" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="L30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" ht="91">
-      <c r="I31" s="1">
+    </row>
+    <row r="31" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J31" s="7" t="s">
@@ -1348,12 +1167,9 @@
       <c r="K31" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="L31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" ht="68.65">
-      <c r="I32" s="1">
+    </row>
+    <row r="32" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J32" s="7" t="s">
@@ -1362,12 +1178,9 @@
       <c r="K32" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" ht="23.85">
-      <c r="I33" s="1">
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J33" s="7" t="s">
@@ -1376,11 +1189,8 @@
       <c r="K33" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" ht="12.8">
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="1" t="s">
         <v>61</v>
       </c>
@@ -1388,18 +1198,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E37" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" ht="79.85">
-      <c r="I41" s="1">
+    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -1408,14 +1218,11 @@
       <c r="K41" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L41" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F42" s="10"/>
     </row>
-    <row r="43" ht="12.8">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="1" t="s">
         <v>66</v>
       </c>
@@ -1423,17 +1230,17 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" ht="12.8">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1" t="s">
         <v>69</v>
       </c>
@@ -1441,14 +1248,14 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F49" s="10"/>
     </row>
-    <row r="50" ht="98.5">
-      <c r="I50" s="1">
+    <row r="50" customFormat="false" ht="98.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="1" t="n">
         <v>14</v>
       </c>
       <c r="J50" s="7" t="s">
@@ -1457,22 +1264,19 @@
       <c r="K50" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="L50" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="52" ht="12.8">
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E52" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="54" ht="12.8">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="56" ht="74.6">
-      <c r="I56" s="1">
+    <row r="56" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="1" t="n">
         <v>15</v>
       </c>
       <c r="J56" s="7" t="s">
@@ -1481,14 +1285,11 @@
       <c r="K56" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="L56" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="57" ht="12.8">
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F57" s="10"/>
     </row>
-    <row r="58" ht="12.8">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E58" s="1" t="s">
         <v>66</v>
       </c>
@@ -1496,7 +1297,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" ht="12.8">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E59" s="1" t="s">
         <v>76</v>
       </c>
@@ -1504,18 +1305,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60" ht="12.8">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E60" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="64" ht="12.8">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="66" ht="46.25">
-      <c r="I66" s="1">
+    <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I66" s="1" t="n">
         <v>16</v>
       </c>
       <c r="J66" s="7" t="s">
@@ -1524,12 +1325,9 @@
       <c r="K66" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="L66" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="67" ht="13.8">
-      <c r="I67" s="1">
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="1" t="n">
         <v>17</v>
       </c>
       <c r="J67" s="9" t="s">
@@ -1538,12 +1336,9 @@
       <c r="K67" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="L67" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" ht="13.8">
-      <c r="I68" s="1">
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I68" s="1" t="n">
         <v>18</v>
       </c>
       <c r="J68" s="9" t="s">
@@ -1552,11 +1347,8 @@
       <c r="K68" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="L68" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="69" ht="12.8">
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E69" s="1" t="s">
         <v>76</v>
       </c>
@@ -1564,8 +1356,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" ht="57.45">
-      <c r="I70" s="1">
+    <row r="70" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I70" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J70" s="7" t="s">
@@ -1574,12 +1366,9 @@
       <c r="K70" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="L70" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="71" ht="13.8">
-      <c r="I71" s="1">
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I71" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J71" s="9" t="s">
@@ -1588,11 +1377,8 @@
       <c r="K71" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="L71" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="72" ht="12.8">
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E72" s="1" t="s">
         <v>61</v>
       </c>
@@ -1600,21 +1386,21 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" ht="13.8">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J73" s="9"/>
     </row>
-    <row r="74" ht="12.8">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E74" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="76" ht="12.8">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="78" ht="13.8">
-      <c r="I78" s="1">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J78" s="9" t="s">
@@ -1623,11 +1409,8 @@
       <c r="K78" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="L78" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="79" ht="13.8">
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E79" s="1" t="s">
         <v>91</v>
       </c>
@@ -1637,11 +1420,11 @@
       <c r="J79" s="9"/>
       <c r="K79" s="5"/>
     </row>
-    <row r="80" ht="13.8">
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G80" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I80" s="1">
+      <c r="I80" s="1" t="n">
         <v>22</v>
       </c>
       <c r="J80" s="9" t="s">
@@ -1650,12 +1433,9 @@
       <c r="K80" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="L80" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="81" ht="35.05">
-      <c r="I81" s="1">
+    </row>
+    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I81" s="1" t="n">
         <v>23</v>
       </c>
       <c r="J81" s="7" t="s">
@@ -1664,11 +1444,8 @@
       <c r="K81" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="L81" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="82" ht="12.8">
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E82" s="1" t="s">
         <v>91</v>
       </c>
@@ -1678,11 +1455,11 @@
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
     </row>
-    <row r="83" ht="13.8">
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G83" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I83" s="1">
+      <c r="I83" s="1" t="n">
         <v>24</v>
       </c>
       <c r="J83" s="9" t="s">
@@ -1691,13 +1468,10 @@
       <c r="K83" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="L83" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="84" ht="46.25">
+    </row>
+    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G84" s="11"/>
-      <c r="I84" s="1">
+      <c r="I84" s="1" t="n">
         <v>25</v>
       </c>
       <c r="J84" s="7" t="s">
@@ -1706,25 +1480,22 @@
       <c r="K84" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="L84" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="85" ht="13.8">
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G85" s="11"/>
       <c r="J85" s="9"/>
       <c r="K85" s="5"/>
     </row>
-    <row r="86" ht="13.8">
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G86" s="11"/>
       <c r="J86" s="9"/>
       <c r="K86" s="5"/>
     </row>
-    <row r="87" ht="13.8">
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G87" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I87" s="1">
+      <c r="I87" s="1" t="n">
         <v>26</v>
       </c>
       <c r="J87" s="9" t="s">
@@ -1733,13 +1504,10 @@
       <c r="K87" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="L87" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="88" ht="13.8">
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G88" s="11"/>
-      <c r="I88" s="1">
+      <c r="I88" s="1" t="n">
         <v>27</v>
       </c>
       <c r="J88" s="9" t="s">
@@ -1748,15 +1516,12 @@
       <c r="K88" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L88" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="89" ht="13.8">
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G89" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I89" s="1">
+      <c r="I89" s="1" t="n">
         <v>28</v>
       </c>
       <c r="J89" s="9" t="s">
@@ -1765,13 +1530,10 @@
       <c r="K89" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="L89" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="90" ht="68.65">
+    </row>
+    <row r="90" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G90" s="11"/>
-      <c r="I90" s="1">
+      <c r="I90" s="1" t="n">
         <v>29</v>
       </c>
       <c r="J90" s="7" t="s">
@@ -1780,39 +1542,36 @@
       <c r="K90" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="L90" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="91" ht="13.8">
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G91" s="11"/>
       <c r="J91" s="9"/>
       <c r="K91" s="5"/>
     </row>
-    <row r="92" ht="13.8">
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G92" s="11"/>
       <c r="J92" s="9"/>
       <c r="K92" s="5"/>
     </row>
-    <row r="93" ht="12.8">
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
     </row>
-    <row r="94" ht="12.8">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E94" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
     </row>
-    <row r="95" ht="13.8">
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G95" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I95" s="1">
+      <c r="I95" s="1" t="n">
         <v>30</v>
       </c>
       <c r="J95" s="12" t="s">
@@ -1821,12 +1580,9 @@
       <c r="K95" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L95" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="96" ht="53.7">
-      <c r="I96" s="1">
+    </row>
+    <row r="96" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I96" s="1" t="n">
         <v>31</v>
       </c>
       <c r="J96" s="7" t="s">
@@ -1835,15 +1591,12 @@
       <c r="K96" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="L96" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="97" ht="13.8">
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G97" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I97" s="1">
+      <c r="I97" s="1" t="n">
         <v>32</v>
       </c>
       <c r="J97" s="12" t="s">
@@ -1852,12 +1605,9 @@
       <c r="K97" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="L97" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="98" ht="13.8">
-      <c r="I98" s="1">
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I98" s="1" t="n">
         <v>33</v>
       </c>
       <c r="J98" s="9" t="s">
@@ -1866,11 +1616,8 @@
       <c r="K98" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="L98" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="99" ht="13.8">
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E99" s="1" t="s">
         <v>91</v>
       </c>
@@ -1880,11 +1627,11 @@
       <c r="J99" s="9"/>
       <c r="K99" s="5"/>
     </row>
-    <row r="100" ht="13.8">
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G100" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I100" s="1">
+      <c r="I100" s="1" t="n">
         <v>34</v>
       </c>
       <c r="J100" s="9" t="s">
@@ -1893,12 +1640,9 @@
       <c r="K100" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="L100" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="101" ht="13.8">
-      <c r="I101" s="1">
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I101" s="1" t="n">
         <v>35</v>
       </c>
       <c r="J101" s="12" t="s">
@@ -1907,15 +1651,12 @@
       <c r="K101" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="L101" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="102" ht="13.8">
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G102" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I102" s="1">
+      <c r="I102" s="1" t="n">
         <v>36</v>
       </c>
       <c r="J102" s="9" t="s">
@@ -1924,12 +1665,9 @@
       <c r="K102" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="L102" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="103" ht="13.8">
-      <c r="I103" s="1">
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I103" s="1" t="n">
         <v>37</v>
       </c>
       <c r="J103" s="12" t="s">
@@ -1938,11 +1676,8 @@
       <c r="K103" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="L103" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="104" ht="13.8">
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E104" s="1" t="s">
         <v>76</v>
       </c>
@@ -1951,8 +1686,8 @@
       </c>
       <c r="J104" s="12"/>
     </row>
-    <row r="105" ht="64.15">
-      <c r="I105" s="1">
+    <row r="105" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I105" s="1" t="n">
         <v>38</v>
       </c>
       <c r="J105" s="7" t="s">
@@ -1961,16 +1696,13 @@
       <c r="K105" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L105" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="106" ht="13.8">
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J106" s="12"/>
       <c r="K106" s="5"/>
     </row>
-    <row r="107" ht="85.05">
-      <c r="I107" s="1">
+    <row r="107" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I107" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J107" s="7" t="s">
@@ -1979,11 +1711,8 @@
       <c r="K107" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="L107" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="108" ht="13.8">
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E108" s="1" t="s">
         <v>61</v>
       </c>
@@ -1992,19 +1721,19 @@
       </c>
       <c r="J108" s="12"/>
     </row>
-    <row r="109" ht="13.8">
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E109" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J109" s="12"/>
     </row>
-    <row r="112" ht="12.8">
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="113" ht="124.6">
-      <c r="I113" s="1">
+    <row r="113" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I113" s="1" t="n">
         <v>42</v>
       </c>
       <c r="J113" s="7" t="s">
@@ -2013,29 +1742,26 @@
       <c r="K113" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="L113" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="115" ht="12.8">
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="1" t="s">
         <v>130</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I12 I22:I27 I20 I34:I40 I57:I65 I72:I77 I42:I55 I69 I104 I107:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28:I33 I41 I70:I71 I105:I106 I13:I19 I56 I66:I68 I78:I103">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/elder_exile.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/elder_exile.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="raphael" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="raphael" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="171">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -487,6 +487,154 @@
   <si>
     <t xml:space="preserve">last</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#race穿过结界到了这个村子…？
+原来如此，是那个小子出的主意吧。嘻嘻嘻…他确实不再需要「手环」了。毕竟就连我们伟大的主人伊兹帕鲁特大人都已经抛弃了他。
+也罢，这村子远离尘世，也总有些自己才知道的麻烦事。如果外人来了能派上些用场，就让他们来吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请和我讲讲伊斯西泽尔吧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你知道伊斯西泽尔吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">发现了迪伯妮但是…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于牛头人的大角</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我带回了迪伯妮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我杀了迪伯妮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迪伯妮不知去了哪里</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暗之畸形「伊斯西泽尔」。嘻嘻嘻…这个村子怎会有人不知道这名字？
+在他的灵魂被不净之物玷污前，可是被誉为最接近神灵的魔法师。
+你们招惹了麻烦的敌人。就算是我们也没有能与他对抗的手段。就算是有办法，我们也不会参与这场世俗的纷争。说到底，流放者只对怎么赎罪感兴趣。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过…嘻嘻嘻…你也不必急着走…，眼下正好有适合交给你这种冒险者做的工作。如果你能顺利完成的话，也可授予你所渴求的「知识」。我们自古传承的秘术的配方，也许能成为用来击退伊斯西泽尔的武器。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘻嘻嘻…好吧，从哪里开始讲呢。
+你知道吗？这个村子的东南方有个叫露里耶的神殿。众神从地上离去之后，露里耶神殿如今只能可悲地沉入海底…在我还是人类的时候，曾在那个神殿生活过。
+神殿里不知从哪里迷路来了一只暴食海狮幼崽，它叫迪伯妮，对我很亲近。虽然是个愚蠢又贪吃的家伙…嘻嘻嘻…但我对那笨拙可爱的小东西倾注了多到不可思议的感情。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后来我迎来了死亡，但因生前的罪孽，我注定要在这个村子里无尽地赎罪。而这都已经是几千年前的事了。
+从那之后已经度过了漫长的岁月。但不可思议的是…哦哦，时至今日，我还感觉得到！迪伯妮还活着！
+嘻嘻嘻…我可以听到，那孩子被遗忘在海底发出的悲鸣。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">希望你能把迪伯妮从那深水之狱中带回来。
+我不知道那孩子依旧是海狮，还是变成了什么怪物…。如果它已经没有了获救的希望，就请你让那只悲伤的野兽永远的安息。这就是我的愿望。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘻嘻嘻…话说回来，它还真是个笨孩子。都有本事活几千年，为什么还要留在那废墟中…嘻嘻嘻…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迪伯妮，变成了巨大的龙…？
+这可真是奇怪…我记得它确实是暴食海狮的幼崽…不对，人类时的记忆，早就淡去了。
+但不管怎么说，变成那种庞然大物，也不容易带回来了吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果用古老的魔道具「龙捕获球」的话，也许可以捕捉到迪伯妮。
+但是…嘻嘻嘻…很不凑巧，这个村子里缺乏制作的材料。
+它需要被称为「牛头人的大角」的稀有素材…说起来，有一群牛头人在约恩村南边筑了巢呢，嘻嘻嘻…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦哦，你拿的那不就是「牛头人的大角」吗？
+嘻嘻嘻…这样就能制作出把迪伯妮带回来的捕获球了。
+捕获球的使用方法，就不用对你这样的冒险者说明了吧。嘻嘻嘻…用手拿着丢向对方就可以。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迪伯妮它…这样啊…既然你觉得应该这么做，我也不说什么了。
+在这几千年的岁月里，那孩子为什么一直留在露里耶的废墟…算了，现在再去追究也没什么意义了。嘻嘻嘻…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘻嘻嘻…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…不用担心。我没有忘记和你的约定。
+﻿
+接下来就把自古传承下来的秘术配方传授给你。卢恩铸造…这是人世间失传已久的宝贵知识。在和伊斯西泽尔的战斗中，它一定能帮到你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我们之间的交易结束了。好了，你可以走了，嘻嘻嘻…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…迪伯妮！　真的是迪伯妮吗！？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咕嗷嗷嗷嗷嗷嗷！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦哦，何等恐怖的咆哮！ 是想吃了我吗…？ 
+嘻嘻嘻…真有精神。我想，你大概已经把我给忘了吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咕嗷嗷嗷嗷嗷嗷嗷嗷嗷嗷！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…没想到，你原来是只龙啊。
+看到你这么精神的样子，我就满足了。老朽这条烂命死不足惜。来吧，随你喜欢吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咕嗷…咕噜噜……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迪伯妮...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咕噜咕噜…咕……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迪伯妮，难道说，你还记得我吗？
+啊…！　你脖子上的蝴蝶结，是我还是人类的时候开玩笑给你戴上的…
+你竟然如此珍惜它…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咕噜…咕噜…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迪伯妮，这样啊…原来是这样啊，嘻嘻嘻…
+我把你留在了海底，自己则被囚禁在无尽的赎罪中。但时隔千年，你还是没有抛弃我吗。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咕噜…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…原谅愚蠢的我吧，迪伯妮。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咕噜……咕嗷嗷嗷……！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦哦，迪伯妮...!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…嘻嘻嘻、不用担心。我没有忘记和你的约定。
+接下来就把自古传承下来的秘术配方传授给你。卢恩铸造…这是从人世间失传已久的宝贵知识。在和伊斯西泽尔的战斗中，它一定能帮到你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好了，迪伯妮。我要快点把你介绍给村里的其他人！
+嘻嘻嘻…不用害怕。大家虽然脸长的很诡异，但都不是坏人。你一定会成为村子里的大明星。
+过来，迪伯妮，来这边。以后我们就一起生活下去，…就像在露里耶的那个时候一样…嘻嘻嘻……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当伊斯西泽尔还是人类的时候，王侯贵族都曾争着乞求他的帮助。嘻嘻嘻…凭他强大的魔力，想支配大地上的王国也仅是不值得一提的小事罢了。
+伊斯西泽尔至今都甘愿在朽烂的古城夜以继日地研究魔石，换句话说，人类世界的权力也好名声也罢，对他而言都与尘埃无异。
+别忘了这点。你们将要面对的敌人，是超脱俗世纷争之人。你们正要叩响神话的大门。</t>
+  </si>
 </sst>
 </file>
 
@@ -506,19 +654,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -537,7 +685,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -570,7 +718,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -579,86 +727,86 @@
     </border>
   </borders>
   <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -668,18 +816,18 @@
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Excel Built-in Normal" xfId="20"/>
+    <cellStyle name="Excel Built-in Normal" xfId="20" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -855,26 +1003,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L115"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="16.55" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -912,24 +1060,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>42</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="79.85">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -938,20 +1086,23 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
@@ -961,7 +1112,7 @@
       <c r="E12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="I12" s="1">
         <v>41</v>
       </c>
       <c r="J12" s="5" t="s">
@@ -970,8 +1121,11 @@
       <c r="K12" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" ht="12.8">
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
@@ -981,7 +1135,7 @@
       <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="I13" s="1">
         <v>2</v>
       </c>
       <c r="J13" s="5" t="s">
@@ -990,8 +1144,11 @@
       <c r="K13" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" ht="12.8">
       <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
@@ -1004,7 +1161,7 @@
       <c r="E14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="1" t="n">
+      <c r="I14" s="1">
         <v>3</v>
       </c>
       <c r="J14" s="5" t="s">
@@ -1013,8 +1170,11 @@
       <c r="K14" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" ht="12.8">
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
@@ -1027,7 +1187,7 @@
       <c r="E15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="I15" s="1">
         <v>4</v>
       </c>
       <c r="J15" s="5" t="s">
@@ -1036,8 +1196,11 @@
       <c r="K15" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" ht="12.8">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -1047,7 +1210,7 @@
       <c r="E16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="1">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -1056,8 +1219,11 @@
       <c r="K16" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
       <c r="B17" s="1" t="s">
         <v>38</v>
       </c>
@@ -1067,7 +1233,7 @@
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>6</v>
       </c>
       <c r="J17" s="5" t="s">
@@ -1076,8 +1242,11 @@
       <c r="K17" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
@@ -1087,7 +1256,7 @@
       <c r="E18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="I18" s="1">
         <v>7</v>
       </c>
       <c r="J18" s="5" t="s">
@@ -1096,12 +1265,15 @@
       <c r="K18" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="E20" s="1" t="s">
         <v>45</v>
       </c>
@@ -1109,23 +1281,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="E22" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="E23" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="12.8">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="1" t="n">
+    <row r="28" ht="113.4">
+      <c r="I28" s="1">
         <v>8</v>
       </c>
       <c r="J28" s="7" t="s">
@@ -1134,9 +1306,12 @@
       <c r="K28" s="8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="1" t="n">
+      <c r="L28" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" ht="13.8">
+      <c r="I29" s="1">
         <v>9</v>
       </c>
       <c r="J29" s="9" t="s">
@@ -1145,9 +1320,12 @@
       <c r="K29" s="6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I30" s="1" t="n">
+      <c r="L29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" ht="113.4">
+      <c r="I30" s="1">
         <v>40</v>
       </c>
       <c r="J30" s="7" t="s">
@@ -1156,9 +1334,12 @@
       <c r="K30" s="8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I31" s="1" t="n">
+      <c r="L30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" ht="91">
+      <c r="I31" s="1">
         <v>10</v>
       </c>
       <c r="J31" s="7" t="s">
@@ -1167,9 +1348,12 @@
       <c r="K31" s="8" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="1" t="n">
+      <c r="L31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" ht="68.65">
+      <c r="I32" s="1">
         <v>11</v>
       </c>
       <c r="J32" s="7" t="s">
@@ -1178,9 +1362,12 @@
       <c r="K32" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I33" s="1" t="n">
+      <c r="L32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" ht="23.85">
+      <c r="I33" s="1">
         <v>12</v>
       </c>
       <c r="J33" s="7" t="s">
@@ -1189,8 +1376,11 @@
       <c r="K33" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" ht="12.8">
       <c r="E34" s="1" t="s">
         <v>61</v>
       </c>
@@ -1198,18 +1388,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="E37" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="A39" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I41" s="1" t="n">
+    <row r="41" ht="79.85">
+      <c r="I41" s="1">
         <v>13</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -1218,11 +1408,14 @@
       <c r="K41" s="8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
       <c r="F42" s="10"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.8">
       <c r="E43" s="1" t="s">
         <v>66</v>
       </c>
@@ -1230,17 +1423,17 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.8">
       <c r="B44" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="A47" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="B48" s="1" t="s">
         <v>69</v>
       </c>
@@ -1248,14 +1441,14 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="A49" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F49" s="10"/>
     </row>
-    <row r="50" customFormat="false" ht="98.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I50" s="1" t="n">
+    <row r="50" ht="98.5">
+      <c r="I50" s="1">
         <v>14</v>
       </c>
       <c r="J50" s="7" t="s">
@@ -1264,19 +1457,22 @@
       <c r="K50" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L50" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" ht="12.8">
       <c r="E52" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.8">
       <c r="A54" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I56" s="1" t="n">
+    <row r="56" ht="74.6">
+      <c r="I56" s="1">
         <v>15</v>
       </c>
       <c r="J56" s="7" t="s">
@@ -1285,11 +1481,14 @@
       <c r="K56" s="8" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L56" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" ht="12.8">
       <c r="F57" s="10"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="12.8">
       <c r="E58" s="1" t="s">
         <v>66</v>
       </c>
@@ -1297,7 +1496,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.8">
       <c r="E59" s="1" t="s">
         <v>76</v>
       </c>
@@ -1305,18 +1504,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="12.8">
       <c r="E60" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" ht="12.8">
       <c r="A64" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I66" s="1" t="n">
+    <row r="66" ht="46.25">
+      <c r="I66" s="1">
         <v>16</v>
       </c>
       <c r="J66" s="7" t="s">
@@ -1325,9 +1524,12 @@
       <c r="K66" s="8" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I67" s="1" t="n">
+      <c r="L66" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" ht="13.8">
+      <c r="I67" s="1">
         <v>17</v>
       </c>
       <c r="J67" s="9" t="s">
@@ -1336,9 +1538,12 @@
       <c r="K67" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I68" s="1" t="n">
+      <c r="L67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" ht="13.8">
+      <c r="I68" s="1">
         <v>18</v>
       </c>
       <c r="J68" s="9" t="s">
@@ -1347,8 +1552,11 @@
       <c r="K68" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L68" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" ht="12.8">
       <c r="E69" s="1" t="s">
         <v>76</v>
       </c>
@@ -1356,8 +1564,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I70" s="1" t="n">
+    <row r="70" ht="57.45">
+      <c r="I70" s="1">
         <v>19</v>
       </c>
       <c r="J70" s="7" t="s">
@@ -1366,9 +1574,12 @@
       <c r="K70" s="8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I71" s="1" t="n">
+      <c r="L70" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" ht="13.8">
+      <c r="I71" s="1">
         <v>20</v>
       </c>
       <c r="J71" s="9" t="s">
@@ -1377,8 +1588,11 @@
       <c r="K71" s="6" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" ht="12.8">
       <c r="E72" s="1" t="s">
         <v>61</v>
       </c>
@@ -1386,21 +1600,21 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="13.8">
       <c r="J73" s="9"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="12.8">
       <c r="E74" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="12.8">
       <c r="A76" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I78" s="1" t="n">
+    <row r="78" ht="13.8">
+      <c r="I78" s="1">
         <v>21</v>
       </c>
       <c r="J78" s="9" t="s">
@@ -1409,8 +1623,11 @@
       <c r="K78" s="6" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L78" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" ht="13.8">
       <c r="E79" s="1" t="s">
         <v>91</v>
       </c>
@@ -1420,11 +1637,11 @@
       <c r="J79" s="9"/>
       <c r="K79" s="5"/>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" ht="13.8">
       <c r="G80" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I80" s="1" t="n">
+      <c r="I80" s="1">
         <v>22</v>
       </c>
       <c r="J80" s="9" t="s">
@@ -1433,9 +1650,12 @@
       <c r="K80" s="6" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I81" s="1" t="n">
+      <c r="L80" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="81" ht="35.05">
+      <c r="I81" s="1">
         <v>23</v>
       </c>
       <c r="J81" s="7" t="s">
@@ -1444,8 +1664,11 @@
       <c r="K81" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L81" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82" ht="12.8">
       <c r="E82" s="1" t="s">
         <v>91</v>
       </c>
@@ -1455,11 +1678,11 @@
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" ht="13.8">
       <c r="G83" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I83" s="1" t="n">
+      <c r="I83" s="1">
         <v>24</v>
       </c>
       <c r="J83" s="9" t="s">
@@ -1468,10 +1691,13 @@
       <c r="K83" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L83" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84" ht="46.25">
       <c r="G84" s="11"/>
-      <c r="I84" s="1" t="n">
+      <c r="I84" s="1">
         <v>25</v>
       </c>
       <c r="J84" s="7" t="s">
@@ -1480,22 +1706,25 @@
       <c r="K84" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L84" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" ht="13.8">
       <c r="G85" s="11"/>
       <c r="J85" s="9"/>
       <c r="K85" s="5"/>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="13.8">
       <c r="G86" s="11"/>
       <c r="J86" s="9"/>
       <c r="K86" s="5"/>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="13.8">
       <c r="G87" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I87" s="1" t="n">
+      <c r="I87" s="1">
         <v>26</v>
       </c>
       <c r="J87" s="9" t="s">
@@ -1504,10 +1733,13 @@
       <c r="K87" s="6" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L87" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="88" ht="13.8">
       <c r="G88" s="11"/>
-      <c r="I88" s="1" t="n">
+      <c r="I88" s="1">
         <v>27</v>
       </c>
       <c r="J88" s="9" t="s">
@@ -1516,12 +1748,15 @@
       <c r="K88" s="6" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L88" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="89" ht="13.8">
       <c r="G89" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I89" s="1" t="n">
+      <c r="I89" s="1">
         <v>28</v>
       </c>
       <c r="J89" s="9" t="s">
@@ -1530,10 +1765,13 @@
       <c r="K89" s="6" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L89" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="90" ht="68.65">
       <c r="G90" s="11"/>
-      <c r="I90" s="1" t="n">
+      <c r="I90" s="1">
         <v>29</v>
       </c>
       <c r="J90" s="7" t="s">
@@ -1542,36 +1780,39 @@
       <c r="K90" s="8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L90" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="91" ht="13.8">
       <c r="G91" s="11"/>
       <c r="J91" s="9"/>
       <c r="K91" s="5"/>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="13.8">
       <c r="G92" s="11"/>
       <c r="J92" s="9"/>
       <c r="K92" s="5"/>
     </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" ht="12.8">
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" ht="12.8">
       <c r="E94" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F94" s="1" t="n">
+      <c r="F94" s="1">
         <v>12</v>
       </c>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
     </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" ht="13.8">
       <c r="G95" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I95" s="1" t="n">
+      <c r="I95" s="1">
         <v>30</v>
       </c>
       <c r="J95" s="12" t="s">
@@ -1580,9 +1821,12 @@
       <c r="K95" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I96" s="1" t="n">
+      <c r="L95" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="96" ht="53.7">
+      <c r="I96" s="1">
         <v>31</v>
       </c>
       <c r="J96" s="7" t="s">
@@ -1591,12 +1835,15 @@
       <c r="K96" s="8" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L96" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="97" ht="13.8">
       <c r="G97" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I97" s="1" t="n">
+      <c r="I97" s="1">
         <v>32</v>
       </c>
       <c r="J97" s="12" t="s">
@@ -1605,9 +1852,12 @@
       <c r="K97" s="6" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I98" s="1" t="n">
+      <c r="L97" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="98" ht="13.8">
+      <c r="I98" s="1">
         <v>33</v>
       </c>
       <c r="J98" s="9" t="s">
@@ -1616,8 +1866,11 @@
       <c r="K98" s="6" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L98" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="99" ht="13.8">
       <c r="E99" s="1" t="s">
         <v>91</v>
       </c>
@@ -1627,11 +1880,11 @@
       <c r="J99" s="9"/>
       <c r="K99" s="5"/>
     </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" ht="13.8">
       <c r="G100" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I100" s="1" t="n">
+      <c r="I100" s="1">
         <v>34</v>
       </c>
       <c r="J100" s="9" t="s">
@@ -1640,9 +1893,12 @@
       <c r="K100" s="6" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I101" s="1" t="n">
+      <c r="L100" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="101" ht="13.8">
+      <c r="I101" s="1">
         <v>35</v>
       </c>
       <c r="J101" s="12" t="s">
@@ -1651,12 +1907,15 @@
       <c r="K101" s="6" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L101" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="102" ht="13.8">
       <c r="G102" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I102" s="1" t="n">
+      <c r="I102" s="1">
         <v>36</v>
       </c>
       <c r="J102" s="9" t="s">
@@ -1665,9 +1924,12 @@
       <c r="K102" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I103" s="1" t="n">
+      <c r="L102" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103" ht="13.8">
+      <c r="I103" s="1">
         <v>37</v>
       </c>
       <c r="J103" s="12" t="s">
@@ -1676,8 +1938,11 @@
       <c r="K103" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L103" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" ht="13.8">
       <c r="E104" s="1" t="s">
         <v>76</v>
       </c>
@@ -1686,8 +1951,8 @@
       </c>
       <c r="J104" s="12"/>
     </row>
-    <row r="105" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I105" s="1" t="n">
+    <row r="105" ht="64.15">
+      <c r="I105" s="1">
         <v>38</v>
       </c>
       <c r="J105" s="7" t="s">
@@ -1696,13 +1961,16 @@
       <c r="K105" s="8" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L105" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="106" ht="13.8">
       <c r="J106" s="12"/>
       <c r="K106" s="5"/>
     </row>
-    <row r="107" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I107" s="1" t="n">
+    <row r="107" ht="85.05">
+      <c r="I107" s="1">
         <v>39</v>
       </c>
       <c r="J107" s="7" t="s">
@@ -1711,8 +1979,11 @@
       <c r="K107" s="8" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L107" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="108" ht="13.8">
       <c r="E108" s="1" t="s">
         <v>61</v>
       </c>
@@ -1721,19 +1992,19 @@
       </c>
       <c r="J108" s="12"/>
     </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" ht="13.8">
       <c r="E109" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J109" s="12"/>
     </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" ht="12.8">
       <c r="A112" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I113" s="1" t="n">
+    <row r="113" ht="124.6">
+      <c r="I113" s="1">
         <v>42</v>
       </c>
       <c r="J113" s="7" t="s">
@@ -1742,26 +2013,29 @@
       <c r="K113" s="8" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L113" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="115" ht="12.8">
       <c r="B115" s="1" t="s">
         <v>130</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I12 I22:I27 I20 I34:I40 I57:I65 I72:I77 I42:I55 I69 I104 I107:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28:I33 I41 I70:I71 I105:I106 I13:I19 I56 I66:I68 I78:I103">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
